--- a/Luban/DataTables/Datas/Item/道具系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/道具系统表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="掉落表" sheetId="5" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
   <si>
     <t>##</t>
   </si>
@@ -141,6 +141,9 @@
     <t>icon</t>
   </si>
   <si>
+    <t>prefab</t>
+  </si>
+  <si>
     <t>道具编号</t>
   </si>
   <si>
@@ -166,6 +169,9 @@
   </si>
   <si>
     <t>道具图标</t>
+  </si>
+  <si>
+    <t>预制体地址</t>
   </si>
   <si>
     <t>1AABBBCCCC形式
@@ -1417,7 +1423,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
@@ -1432,7 +1438,7 @@
     <col min="12" max="12" width="20.2083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:12">
+    <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1469,68 +1475,75 @@
       <c r="L1" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" ht="87" spans="1:12">
+      <c r="M1" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" ht="87" spans="1:13">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="I2" s="4" t="s">
         <v>6</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:12">
+        <v>34</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="114" spans="1:13">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" ht="28.5" spans="1:12">
+        <v>39</v>
+      </c>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" ht="28.5" spans="1:13">
       <c r="A4" s="8" t="s">
         <v>10</v>
       </c>
@@ -1541,10 +1554,10 @@
         <v>110001</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F4" s="8">
         <v>1</v>
@@ -1565,10 +1578,10 @@
         <v>1</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:12">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:13">
       <c r="A5" s="8" t="s">
         <v>10</v>
       </c>
@@ -1579,10 +1592,10 @@
         <v>110002</v>
       </c>
       <c r="D5" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>41</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="F5" s="8">
         <v>1</v>
@@ -1603,10 +1616,10 @@
         <v>1</v>
       </c>
       <c r="L5" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5" spans="1:12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:13">
       <c r="A6" s="8"/>
       <c r="B6" s="8">
         <v>110003</v>
@@ -1615,10 +1628,10 @@
         <v>110003</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" s="8">
         <v>1</v>
@@ -1639,10 +1652,10 @@
         <v>1</v>
       </c>
       <c r="L6" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:12">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:13">
       <c r="A7" s="8"/>
       <c r="B7" s="8">
         <v>110004</v>
@@ -1651,10 +1664,10 @@
         <v>110004</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7" s="8">
         <v>1</v>
@@ -1675,10 +1688,10 @@
         <v>1</v>
       </c>
       <c r="L7" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:13">
       <c r="A8" s="8"/>
       <c r="B8" s="8">
         <v>110005</v>
@@ -1687,10 +1700,10 @@
         <v>110005</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F8" s="8">
         <v>1</v>
@@ -1711,12 +1724,12 @@
         <v>1</v>
       </c>
       <c r="L8" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B9" s="8">
         <v>110006</v>
@@ -1725,10 +1738,10 @@
         <v>110006</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F9" s="8">
         <v>1</v>
@@ -1749,12 +1762,12 @@
         <v>1</v>
       </c>
       <c r="L9" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" s="9" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B10" s="8">
         <v>110007</v>
@@ -1763,10 +1776,10 @@
         <v>110007</v>
       </c>
       <c r="D10" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E10" s="8" t="s">
         <v>51</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="F10" s="8">
         <v>1</v>
@@ -1787,12 +1800,12 @@
         <v>1</v>
       </c>
       <c r="L10" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10 E4:E9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E10">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/道具系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/道具系统表.xlsx
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
   <si>
     <t>##</t>
   </si>
@@ -114,6 +114,9 @@
     <t>name</t>
   </si>
   <si>
+    <t>category</t>
+  </si>
+  <si>
     <t>name_cn</t>
   </si>
   <si>
@@ -178,6 +181,9 @@
 AA表示道具类别编号
 BBB表示道具子类编号
 CCCC表示编号</t>
+  </si>
+  <si>
+    <t>分类</t>
   </si>
   <si>
     <t>参见道具类别备注</t>
@@ -910,6 +916,9 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -927,9 +936,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1283,7 +1289,7 @@
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="14" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
@@ -1297,8 +1303,8 @@
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="14"/>
-      <c r="C3" s="14" t="s">
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="7" t="s">
@@ -1306,112 +1312,112 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="9">
         <v>10001</v>
       </c>
-      <c r="C4" s="8" t="s">
+      <c r="C4" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="9">
+      <c r="B5" s="10">
         <v>10002</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="9">
+      <c r="B6" s="10">
         <v>10003</v>
       </c>
-      <c r="C6" s="8" t="s">
+      <c r="C6" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="9">
+      <c r="D6" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="9"/>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="9"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="9"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
     </row>
     <row r="14" spans="1:4">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="8"/>
-      <c r="B15" s="8"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="8"/>
-      <c r="B16" s="8"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="8"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="8"/>
-      <c r="B17" s="8"/>
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1423,22 +1429,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12.9333333333333" customWidth="1"/>
     <col min="3" max="3" width="9.44166666666667" customWidth="1"/>
-    <col min="4" max="4" width="8.375" customWidth="1"/>
-    <col min="5" max="5" width="7.175" customWidth="1"/>
-    <col min="6" max="8" width="8.9" customWidth="1"/>
-    <col min="9" max="9" width="11.6333333333333" customWidth="1"/>
-    <col min="10" max="10" width="9.45" customWidth="1"/>
-    <col min="11" max="11" width="13.6916666666667" customWidth="1"/>
-    <col min="12" max="12" width="20.2083333333333" customWidth="1"/>
+    <col min="4" max="5" width="8.375" customWidth="1"/>
+    <col min="6" max="6" width="7.175" customWidth="1"/>
+    <col min="7" max="9" width="8.9" customWidth="1"/>
+    <col min="10" max="10" width="11.6333333333333" customWidth="1"/>
+    <col min="11" max="11" width="9.45" customWidth="1"/>
+    <col min="12" max="12" width="13.6916666666667" customWidth="1"/>
+    <col min="13" max="13" width="20.2083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:13">
+    <row r="1" s="1" customFormat="1" spans="1:14">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1478,21 +1484,22 @@
       <c r="M1" s="3" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="2" ht="87" spans="1:13">
+      <c r="N1" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" ht="87" spans="1:14">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" s="5"/>
-      <c r="E2" s="5" t="s">
-        <v>28</v>
-      </c>
+      <c r="E2" s="5"/>
       <c r="F2" s="5" t="s">
         <v>29</v>
       </c>
@@ -1502,11 +1509,11 @@
       <c r="H2" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>33</v>
@@ -1517,295 +1524,308 @@
       <c r="M2" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:13">
+      <c r="N2" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" s="2" customFormat="1" ht="114" spans="1:14">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="F3" s="7"/>
+      <c r="D3" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="G3" s="7"/>
-      <c r="H3" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="I3" s="7"/>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7" t="s">
+        <v>40</v>
+      </c>
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="M3" s="7"/>
-    </row>
-    <row r="4" ht="28.5" spans="1:13">
-      <c r="A4" s="8" t="s">
+      <c r="L3" s="7"/>
+      <c r="M3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="7"/>
+    </row>
+    <row r="4" ht="28.5" spans="1:14">
+      <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="8">
+      <c r="B4" s="9">
         <v>110001</v>
       </c>
-      <c r="C4" s="8">
+      <c r="C4" s="9">
         <v>110001</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F4" s="8">
-        <v>1</v>
-      </c>
-      <c r="G4" s="8">
-        <v>1</v>
-      </c>
-      <c r="H4" s="8">
+      <c r="D4" s="9"/>
+      <c r="E4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="9">
+        <v>1</v>
+      </c>
+      <c r="H4" s="9">
+        <v>1</v>
+      </c>
+      <c r="I4" s="9">
         <v>110001</v>
       </c>
-      <c r="I4" s="9">
-        <v>1</v>
-      </c>
-      <c r="J4" s="9">
-        <v>1</v>
-      </c>
-      <c r="K4" s="9">
-        <v>1</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:13">
-      <c r="A5" s="8" t="s">
+      <c r="J4" s="10">
+        <v>1</v>
+      </c>
+      <c r="K4" s="10">
+        <v>1</v>
+      </c>
+      <c r="L4" s="10">
+        <v>1</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:14">
+      <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="8">
+      <c r="B5" s="9">
         <v>110002</v>
       </c>
-      <c r="C5" s="8">
+      <c r="C5" s="9">
         <v>110002</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="12"/>
+      <c r="E5" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="8">
-        <v>1</v>
-      </c>
-      <c r="G5" s="8">
-        <v>1</v>
-      </c>
-      <c r="H5" s="8">
+      <c r="G5" s="9">
+        <v>1</v>
+      </c>
+      <c r="H5" s="9">
+        <v>1</v>
+      </c>
+      <c r="I5" s="9">
         <v>110002</v>
       </c>
-      <c r="I5" s="9">
-        <v>1</v>
-      </c>
-      <c r="J5" s="9">
-        <v>1</v>
-      </c>
-      <c r="K5" s="9">
-        <v>1</v>
-      </c>
-      <c r="L5" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5" spans="1:13">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
+      <c r="J5" s="10">
+        <v>1</v>
+      </c>
+      <c r="K5" s="10">
+        <v>1</v>
+      </c>
+      <c r="L5" s="10">
+        <v>1</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:14">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9">
         <v>110003</v>
       </c>
-      <c r="C6" s="8">
+      <c r="C6" s="9">
         <v>110003</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="8">
-        <v>1</v>
-      </c>
-      <c r="G6" s="8">
-        <v>1</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="D6" s="12"/>
+      <c r="E6" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G6" s="9">
+        <v>1</v>
+      </c>
+      <c r="H6" s="9">
+        <v>1</v>
+      </c>
+      <c r="I6" s="9">
         <v>110003</v>
       </c>
-      <c r="I6" s="9">
-        <v>1</v>
-      </c>
-      <c r="J6" s="9">
-        <v>1</v>
-      </c>
-      <c r="K6" s="9">
-        <v>1</v>
-      </c>
-      <c r="L6" s="10" t="s">
+      <c r="J6" s="10">
+        <v>1</v>
+      </c>
+      <c r="K6" s="10">
+        <v>1</v>
+      </c>
+      <c r="L6" s="10">
+        <v>1</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:14">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9">
+        <v>110004</v>
+      </c>
+      <c r="C7" s="9">
+        <v>110004</v>
+      </c>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G7" s="9">
+        <v>1</v>
+      </c>
+      <c r="H7" s="9">
+        <v>1</v>
+      </c>
+      <c r="I7" s="9">
+        <v>110004</v>
+      </c>
+      <c r="J7" s="10">
+        <v>1</v>
+      </c>
+      <c r="K7" s="10">
+        <v>1</v>
+      </c>
+      <c r="L7" s="10">
+        <v>1</v>
+      </c>
+      <c r="M7" s="11" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="1:13">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8">
-        <v>110004</v>
-      </c>
-      <c r="C7" s="8">
-        <v>110004</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F7" s="8">
-        <v>1</v>
-      </c>
-      <c r="G7" s="8">
-        <v>1</v>
-      </c>
-      <c r="H7" s="8">
-        <v>110004</v>
-      </c>
-      <c r="I7" s="9">
-        <v>1</v>
-      </c>
-      <c r="J7" s="9">
-        <v>1</v>
-      </c>
-      <c r="K7" s="9">
-        <v>1</v>
-      </c>
-      <c r="L7" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:13">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
+    <row r="8" ht="28.5" spans="1:14">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9">
         <v>110005</v>
       </c>
-      <c r="C8" s="8">
+      <c r="C8" s="9">
         <v>110005</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="8">
-        <v>1</v>
-      </c>
-      <c r="G8" s="8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="8">
+      <c r="D8" s="12"/>
+      <c r="E8" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="9">
+        <v>1</v>
+      </c>
+      <c r="H8" s="9">
+        <v>1</v>
+      </c>
+      <c r="I8" s="9">
         <v>110005</v>
       </c>
-      <c r="I8" s="9">
-        <v>1</v>
-      </c>
-      <c r="J8" s="9">
-        <v>1</v>
-      </c>
-      <c r="K8" s="9">
-        <v>1</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B9" s="8">
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
+      <c r="K8" s="10">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10">
+        <v>1</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="9">
         <v>110006</v>
       </c>
-      <c r="C9" s="8">
+      <c r="C9" s="9">
         <v>110006</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9" s="8" t="s">
+      <c r="D9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" s="9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="9">
+        <v>1</v>
+      </c>
+      <c r="I9" s="9">
+        <v>110006</v>
+      </c>
+      <c r="J9" s="10">
+        <v>1</v>
+      </c>
+      <c r="K9" s="10">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10">
+        <v>1</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="F9" s="8">
-        <v>1</v>
-      </c>
-      <c r="G9" s="8">
-        <v>1</v>
-      </c>
-      <c r="H9" s="8">
-        <v>110006</v>
-      </c>
-      <c r="I9" s="9">
-        <v>1</v>
-      </c>
-      <c r="J9" s="9">
-        <v>1</v>
-      </c>
-      <c r="K9" s="9">
-        <v>1</v>
-      </c>
-      <c r="L9" s="10" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="8">
+      <c r="B10" s="9">
         <v>110007</v>
       </c>
-      <c r="C10" s="8">
+      <c r="C10" s="9">
         <v>110007</v>
       </c>
-      <c r="D10" s="12" t="s">
+      <c r="D10" s="13"/>
+      <c r="E10" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8">
-        <v>1</v>
-      </c>
-      <c r="H10" s="8">
+      <c r="G10" s="9">
+        <v>1</v>
+      </c>
+      <c r="H10" s="9">
+        <v>1</v>
+      </c>
+      <c r="I10" s="9">
         <v>110007</v>
       </c>
-      <c r="I10" s="9">
-        <v>1</v>
-      </c>
-      <c r="J10" s="9">
-        <v>1</v>
-      </c>
-      <c r="K10" s="9">
-        <v>1</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>54</v>
+      <c r="J10" s="10">
+        <v>1</v>
+      </c>
+      <c r="K10" s="10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10">
+        <v>1</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F10">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/道具系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/道具系统表.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Projects\Unity\ProjectTinyRpg\Luban\DataTables\Datas\Item\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610" activeTab="1"/>
   </bookViews>
@@ -45,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
   <si>
     <t>##</t>
   </si>
@@ -111,9 +116,6 @@
     <t>id</t>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>category</t>
   </si>
   <si>
@@ -123,15 +125,6 @@
     <t>type</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
     <t>rarity</t>
   </si>
   <si>
@@ -150,19 +143,7 @@
     <t>道具编号</t>
   </si>
   <si>
-    <t>道具名称</t>
-  </si>
-  <si>
     <t>道具类别</t>
-  </si>
-  <si>
-    <t xml:space="preserve">装备占格x </t>
-  </si>
-  <si>
-    <t xml:space="preserve">装备占格y </t>
-  </si>
-  <si>
-    <t>备注</t>
   </si>
   <si>
     <t>可堆叠</t>
@@ -187,9 +168,6 @@
   </si>
   <si>
     <t>参见道具类别备注</t>
-  </si>
-  <si>
-    <t>描述</t>
   </si>
   <si>
     <t>资源路径位于？？？</t>
@@ -1429,22 +1407,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" customWidth="1"/>
     <col min="2" max="2" width="12.9333333333333" customWidth="1"/>
-    <col min="3" max="3" width="9.44166666666667" customWidth="1"/>
-    <col min="4" max="5" width="8.375" customWidth="1"/>
-    <col min="6" max="6" width="7.175" customWidth="1"/>
-    <col min="7" max="9" width="8.9" customWidth="1"/>
-    <col min="10" max="10" width="11.6333333333333" customWidth="1"/>
-    <col min="11" max="11" width="9.45" customWidth="1"/>
-    <col min="12" max="12" width="13.6916666666667" customWidth="1"/>
-    <col min="13" max="13" width="20.2083333333333" customWidth="1"/>
+    <col min="3" max="3" width="8.375" customWidth="1"/>
+    <col min="4" max="4" width="10.875" customWidth="1"/>
+    <col min="5" max="5" width="7.175" customWidth="1"/>
+    <col min="6" max="6" width="11.6333333333333" customWidth="1"/>
+    <col min="7" max="7" width="9.45" customWidth="1"/>
+    <col min="8" max="8" width="13.6916666666667" customWidth="1"/>
+    <col min="9" max="9" width="20.2083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:14">
+    <row r="1" s="1" customFormat="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1475,357 +1452,243 @@
       <c r="J1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" ht="87" spans="1:14">
+    </row>
+    <row r="2" ht="87" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="L2" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="N2" s="4" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" s="2" customFormat="1" ht="114" spans="1:14">
+    </row>
+    <row r="3" s="2" customFormat="1" ht="114" spans="1:10">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" s="7"/>
-    </row>
-    <row r="4" ht="28.5" spans="1:14">
+    </row>
+    <row r="4" ht="28.5" spans="1:10">
       <c r="A4" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="9">
         <v>110001</v>
       </c>
-      <c r="C4" s="9">
-        <v>110001</v>
-      </c>
-      <c r="D4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9" t="s">
+        <v>33</v>
+      </c>
       <c r="E4" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G4" s="9">
-        <v>1</v>
-      </c>
-      <c r="H4" s="9">
-        <v>1</v>
-      </c>
-      <c r="I4" s="9">
-        <v>110001</v>
-      </c>
-      <c r="J4" s="10">
-        <v>1</v>
-      </c>
-      <c r="K4" s="10">
-        <v>1</v>
-      </c>
-      <c r="L4" s="10">
-        <v>1</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" ht="28.5" spans="1:14">
+        <v>34</v>
+      </c>
+      <c r="F4" s="10">
+        <v>1</v>
+      </c>
+      <c r="G4" s="10">
+        <v>1</v>
+      </c>
+      <c r="H4" s="10">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" ht="28.5" spans="1:10">
       <c r="A5" s="9" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="9">
         <v>110002</v>
       </c>
-      <c r="C5" s="9">
-        <v>110002</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="F5" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="9">
-        <v>1</v>
-      </c>
-      <c r="H5" s="9">
-        <v>1</v>
-      </c>
-      <c r="I5" s="9">
-        <v>110002</v>
-      </c>
-      <c r="J5" s="10">
-        <v>1</v>
-      </c>
-      <c r="K5" s="10">
-        <v>1</v>
-      </c>
-      <c r="L5" s="10">
-        <v>1</v>
-      </c>
-      <c r="M5" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="6" ht="28.5" spans="1:14">
+      <c r="C5" s="12"/>
+      <c r="D5" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" ht="28.5" spans="1:10">
       <c r="A6" s="9"/>
       <c r="B6" s="9">
         <v>110003</v>
       </c>
-      <c r="C6" s="9">
-        <v>110003</v>
-      </c>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F6" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G6" s="9">
-        <v>1</v>
-      </c>
-      <c r="H6" s="9">
-        <v>1</v>
-      </c>
-      <c r="I6" s="9">
-        <v>110003</v>
-      </c>
-      <c r="J6" s="10">
-        <v>1</v>
-      </c>
-      <c r="K6" s="10">
-        <v>1</v>
-      </c>
-      <c r="L6" s="10">
-        <v>1</v>
-      </c>
-      <c r="M6" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="7" ht="28.5" spans="1:14">
+      <c r="C6" s="12"/>
+      <c r="D6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F6" s="10">
+        <v>1</v>
+      </c>
+      <c r="G6" s="10">
+        <v>1</v>
+      </c>
+      <c r="H6" s="10">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" ht="28.5" spans="1:10">
       <c r="A7" s="9"/>
       <c r="B7" s="9">
         <v>110004</v>
       </c>
-      <c r="C7" s="9">
-        <v>110004</v>
-      </c>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="9">
-        <v>1</v>
-      </c>
-      <c r="H7" s="9">
-        <v>1</v>
-      </c>
-      <c r="I7" s="9">
-        <v>110004</v>
-      </c>
-      <c r="J7" s="10">
-        <v>1</v>
-      </c>
-      <c r="K7" s="10">
-        <v>1</v>
-      </c>
-      <c r="L7" s="10">
-        <v>1</v>
-      </c>
-      <c r="M7" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="8" ht="28.5" spans="1:14">
+      <c r="C7" s="12"/>
+      <c r="D7" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="8" ht="28.5" spans="1:10">
       <c r="A8" s="9"/>
       <c r="B8" s="9">
         <v>110005</v>
       </c>
-      <c r="C8" s="9">
-        <v>110005</v>
-      </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="9">
-        <v>1</v>
-      </c>
-      <c r="H8" s="9">
-        <v>1</v>
-      </c>
-      <c r="I8" s="9">
-        <v>110005</v>
-      </c>
-      <c r="J8" s="10">
-        <v>1</v>
-      </c>
-      <c r="K8" s="10">
-        <v>1</v>
-      </c>
-      <c r="L8" s="10">
-        <v>1</v>
-      </c>
-      <c r="M8" s="11" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="C8" s="12"/>
+      <c r="D8" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B9" s="9">
         <v>110006</v>
       </c>
-      <c r="C9" s="9">
-        <v>110006</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G9" s="9">
-        <v>1</v>
-      </c>
-      <c r="H9" s="9">
-        <v>1</v>
-      </c>
-      <c r="I9" s="9">
-        <v>110006</v>
-      </c>
-      <c r="J9" s="10">
-        <v>1</v>
-      </c>
-      <c r="K9" s="10">
-        <v>1</v>
-      </c>
-      <c r="L9" s="10">
-        <v>1</v>
-      </c>
-      <c r="M9" s="11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="C9" s="13"/>
+      <c r="D9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="10">
+        <v>1</v>
+      </c>
+      <c r="G9" s="10">
+        <v>1</v>
+      </c>
+      <c r="H9" s="10">
+        <v>1</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" s="10" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B10" s="9">
         <v>110007</v>
       </c>
-      <c r="C10" s="9">
-        <v>110007</v>
-      </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="G10" s="9">
-        <v>1</v>
-      </c>
-      <c r="H10" s="9">
-        <v>1</v>
-      </c>
-      <c r="I10" s="9">
-        <v>110007</v>
-      </c>
-      <c r="J10" s="10">
-        <v>1</v>
-      </c>
-      <c r="K10" s="10">
-        <v>1</v>
-      </c>
-      <c r="L10" s="10">
-        <v>1</v>
-      </c>
-      <c r="M10" s="11" t="s">
-        <v>56</v>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F10">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E4:E10">
       <formula1>#REF!</formula1>
     </dataValidation>
   </dataValidations>

--- a/Luban/DataTables/Datas/Item/道具系统表.xlsx
+++ b/Luban/DataTables/Datas/Item/道具系统表.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="610"/>
   </bookViews>
   <sheets>
     <sheet name="掉落表" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="45">
   <si>
     <t>##</t>
   </si>
@@ -58,19 +58,22 @@
     <t>drop_id</t>
   </si>
   <si>
-    <t>drops</t>
-  </si>
-  <si>
-    <t>darity</t>
+    <t>*drops</t>
   </si>
   <si>
     <t>掉落id</t>
   </si>
   <si>
-    <t>功能编号</t>
-  </si>
-  <si>
-    <t>品质</t>
+    <t>item_id</t>
+  </si>
+  <si>
+    <t>min</t>
+  </si>
+  <si>
+    <t>max</t>
+  </si>
+  <si>
+    <t>chance</t>
   </si>
   <si>
     <r>
@@ -95,24 +98,9 @@
     </r>
   </si>
   <si>
-    <t>itemid-min-max-chance seq,</t>
-  </si>
-  <si>
-    <t>使用的文本显示</t>
-  </si>
-  <si>
     <t>是</t>
   </si>
   <si>
-    <t>540001-1-1-100,560001-1-1-100</t>
-  </si>
-  <si>
-    <t>540001-1-1-100,540002-1-1-100,560001-1-1-100,530001-1-1-100,550001-1-1-100,110006-1-2-100,110007-1-2-100</t>
-  </si>
-  <si>
-    <t>530001-1-1-100,550001-1-1-100,110006-1-2-100,110007-1-2-100</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
@@ -144,6 +132,9 @@
   </si>
   <si>
     <t>道具类别</t>
+  </si>
+  <si>
+    <t>品质</t>
   </si>
   <si>
     <t>可堆叠</t>
@@ -600,7 +591,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -612,6 +603,43 @@
       <left style="thin">
         <color auto="1"/>
       </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -745,7 +773,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -757,34 +785,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -873,7 +901,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -912,8 +940,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="51">
@@ -1241,163 +1281,228 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="2" max="2" width="29.3833333333333" customWidth="1"/>
-    <col min="3" max="3" width="35.375" customWidth="1"/>
-    <col min="4" max="4" width="11.1333333333333" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
+    <col min="4" max="4" width="17.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:6">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" ht="58.5" spans="1:4">
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="16"/>
+    </row>
+    <row r="2" ht="58.5" spans="1:6">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="17" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="18" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" ht="30" spans="1:4">
+      <c r="F2" s="18" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" ht="30" spans="1:6">
       <c r="A3" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="8"/>
-      <c r="C3" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7" t="s">
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="9" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="9" t="s">
-        <v>10</v>
       </c>
       <c r="B4" s="9">
         <v>10001</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>11</v>
+      <c r="C4" s="9">
+        <v>540001</v>
       </c>
       <c r="D4" s="9">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="10">
+      <c r="E4" s="9">
+        <v>1</v>
+      </c>
+      <c r="F4" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="9"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="9">
+        <v>560001</v>
+      </c>
+      <c r="D5" s="9">
+        <v>1</v>
+      </c>
+      <c r="E5" s="9">
+        <v>1</v>
+      </c>
+      <c r="F5" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="10">
         <v>10002</v>
       </c>
-      <c r="C5" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="B6" s="10">
+      <c r="C6" s="9">
+        <v>110006</v>
+      </c>
+      <c r="D6" s="9">
+        <v>1</v>
+      </c>
+      <c r="E6" s="9">
+        <v>1</v>
+      </c>
+      <c r="F6" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="10">
         <v>10003</v>
       </c>
-      <c r="C6" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-    </row>
-    <row r="8" spans="1:4">
+      <c r="C7" s="9">
+        <v>110007</v>
+      </c>
+      <c r="D7" s="9">
+        <v>1</v>
+      </c>
+      <c r="E7" s="9">
+        <v>1</v>
+      </c>
+      <c r="F7" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="9"/>
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="9"/>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9"/>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="9"/>
+      <c r="F9" s="9"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="9"/>
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="9"/>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="9"/>
+      <c r="F10" s="9"/>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="9"/>
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="9"/>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="9"/>
+      <c r="F11" s="9"/>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="9"/>
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="9"/>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="9"/>
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="9"/>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="9"/>
+      <c r="F13" s="9"/>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="9"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="9"/>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="9"/>
+      <c r="F14" s="9"/>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="9"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
       <c r="D15" s="9"/>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="9"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
       <c r="D16" s="9"/>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="9"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
       <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1:F1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1426,96 +1531,96 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" ht="87" spans="1:10">
+    </row>
+    <row r="2" ht="72.75" spans="1:10">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
       <c r="E2" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="G2" s="4" t="s">
+      <c r="J2" s="4" t="s">
         <v>25</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="J2" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="114" spans="1:10">
       <c r="A3" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="J3" s="7"/>
     </row>
     <row r="4" ht="28.5" spans="1:10">
       <c r="A4" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="9">
         <v>110001</v>
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F4" s="10">
         <v>1</v>
@@ -1527,34 +1632,34 @@
         <v>1</v>
       </c>
       <c r="I4" s="11" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" ht="28.5" spans="1:10">
       <c r="A5" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" s="9">
         <v>110002</v>
       </c>
       <c r="C5" s="12"/>
       <c r="D5" s="12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E5" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="10">
+        <v>1</v>
+      </c>
+      <c r="G5" s="10">
+        <v>1</v>
+      </c>
+      <c r="H5" s="10">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="F5" s="10">
-        <v>1</v>
-      </c>
-      <c r="G5" s="10">
-        <v>1</v>
-      </c>
-      <c r="H5" s="10">
-        <v>1</v>
-      </c>
-      <c r="I5" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="6" ht="28.5" spans="1:10">
@@ -1564,10 +1669,10 @@
       </c>
       <c r="C6" s="12"/>
       <c r="D6" s="12" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F6" s="10">
         <v>1</v>
@@ -1579,7 +1684,7 @@
         <v>1</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="28.5" spans="1:10">
@@ -1589,22 +1694,22 @@
       </c>
       <c r="C7" s="12"/>
       <c r="D7" s="12" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E7" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="10">
+        <v>1</v>
+      </c>
+      <c r="G7" s="10">
+        <v>1</v>
+      </c>
+      <c r="H7" s="10">
+        <v>1</v>
+      </c>
+      <c r="I7" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="F7" s="10">
-        <v>1</v>
-      </c>
-      <c r="G7" s="10">
-        <v>1</v>
-      </c>
-      <c r="H7" s="10">
-        <v>1</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8" ht="28.5" spans="1:10">
@@ -1614,37 +1719,37 @@
       </c>
       <c r="C8" s="12"/>
       <c r="D8" s="12" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="10">
+        <v>1</v>
+      </c>
+      <c r="G8" s="10">
+        <v>1</v>
+      </c>
+      <c r="H8" s="10">
+        <v>1</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>34</v>
-      </c>
-      <c r="F8" s="10">
-        <v>1</v>
-      </c>
-      <c r="G8" s="10">
-        <v>1</v>
-      </c>
-      <c r="H8" s="10">
-        <v>1</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B9" s="9">
         <v>110006</v>
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="F9" s="10">
         <v>1</v>
@@ -1656,34 +1761,34 @@
         <v>1</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="10" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B10" s="9">
         <v>110007</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E10" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="10">
+        <v>1</v>
+      </c>
+      <c r="G10" s="10">
+        <v>1</v>
+      </c>
+      <c r="H10" s="10">
+        <v>1</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>44</v>
-      </c>
-      <c r="F10" s="10">
-        <v>1</v>
-      </c>
-      <c r="G10" s="10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="10">
-        <v>1</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
